--- a/buchstudium/buchstudium.xlsx
+++ b/buchstudium/buchstudium.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\archive\github\theokratie\buchstudium\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9E92C4-B6EE-4204-A4BF-80CCA309B84E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEFB45C3-B0FC-434D-B2F9-7B5E7C8566F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29400" yWindow="510" windowWidth="18330" windowHeight="14730" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5070" yWindow="975" windowWidth="18330" windowHeight="14730" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="bookstudy" sheetId="1" r:id="rId1"/>
+    <sheet name="buchstudium" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="85">
   <si>
     <t>wcg</t>
   </si>
@@ -39,45 +39,24 @@
     <t>lfb</t>
   </si>
   <si>
-    <t>Lessons you can learn from the Bible</t>
-  </si>
-  <si>
     <t>bt</t>
   </si>
   <si>
-    <t>“Bearing Thorough Witness” About God’s Kingdom</t>
-  </si>
-  <si>
     <t>lff</t>
   </si>
   <si>
-    <t>"Enjoy Life Forever! - An Interactive Bible Course"</t>
-  </si>
-  <si>
     <t>rr</t>
   </si>
   <si>
-    <t>Pure Worship of Jehovah​—Restored At Last!</t>
-  </si>
-  <si>
     <t>jy</t>
   </si>
   <si>
-    <t>Jesus​—The Way, the Truth, the Life</t>
-  </si>
-  <si>
     <t>kr</t>
   </si>
   <si>
-    <t>God’s Kingdom Rules!</t>
-  </si>
-  <si>
     <t>ia</t>
   </si>
   <si>
-    <t>Imitate Their Faith</t>
-  </si>
-  <si>
     <t>cl</t>
   </si>
   <si>
@@ -87,36 +66,18 @@
     <t>jl</t>
   </si>
   <si>
-    <t>What is God's Will?</t>
-  </si>
-  <si>
     <t>jr</t>
   </si>
   <si>
-    <t>God’s Word for Us Through Jeremiah</t>
-  </si>
-  <si>
-    <t>meeting 25 minutes</t>
-  </si>
-  <si>
     <t>cf</t>
   </si>
   <si>
-    <t>“Come Be My Follower”</t>
-  </si>
-  <si>
-    <t>integrated in midweek</t>
-  </si>
-  <si>
     <t>lv</t>
   </si>
   <si>
     <t>“Keep Yourselves in God’s Love”</t>
   </si>
   <si>
-    <t>congregation bible study</t>
-  </si>
-  <si>
     <t>jd</t>
   </si>
   <si>
@@ -289,6 +250,39 @@
   </si>
   <si>
     <t>Geh mutig deinen Weg mit Gott</t>
+  </si>
+  <si>
+    <t>Was wir aus der Bibel lernen können</t>
+  </si>
+  <si>
+    <t>Legt gründlich Zeugnis ab für Gottes Königreich</t>
+  </si>
+  <si>
+    <t>Glücklich – für immer. Ein interaktiver Bibelkurs</t>
+  </si>
+  <si>
+    <t>Die reine Anbetung Jehovas – endlich wiederhergestellt!</t>
+  </si>
+  <si>
+    <t>Jesus — der Weg, die Wahrheit, das Leben</t>
+  </si>
+  <si>
+    <t>Gottes Königreich regiert!</t>
+  </si>
+  <si>
+    <t>Ahmt ihren Glauben nach</t>
+  </si>
+  <si>
+    <t>Komm Jehova doch näher</t>
+  </si>
+  <si>
+    <t>Der Wille Jehovas: Wer lebt heute danach?</t>
+  </si>
+  <si>
+    <t>Was Gott uns durch Jeremia sagen lässt</t>
+  </si>
+  <si>
+    <t>„Komm, folge mir nach“</t>
   </si>
 </sst>
 </file>
@@ -356,10 +350,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -493,41 +487,41 @@
   <cols>
     <col min="1" max="1" width="10.42578125" customWidth="1"/>
     <col min="2" max="2" width="5.42578125" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="3" max="3" width="47.85546875" customWidth="1"/>
     <col min="4" max="4" width="6.42578125" customWidth="1"/>
     <col min="5" max="5" width="8.5703125" customWidth="1"/>
-    <col min="6" max="6" width="30.42578125" customWidth="1"/>
+    <col min="6" max="6" width="31.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>46223</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>86</v>
+      <c r="C2" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="D2" s="2">
         <v>260</v>
@@ -535,19 +529,17 @@
       <c r="E2" s="2">
         <v>54</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="F2" s="1"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>45824</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="D3" s="2">
         <v>240</v>
@@ -555,19 +547,17 @@
       <c r="E3" s="2">
         <v>103</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="F3" s="1"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>45222</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>4</v>
+      <c r="B4" s="6" t="s">
+        <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="D4" s="2">
         <v>224</v>
@@ -575,19 +565,17 @@
       <c r="E4" s="2">
         <v>28</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>44676</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>6</v>
+      <c r="B5" s="6" t="s">
+        <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="D5" s="2">
         <v>256</v>
@@ -595,19 +583,17 @@
       <c r="E5" s="2">
         <v>60</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>44151</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>8</v>
+      <c r="B6" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="D6" s="2">
         <v>240</v>
@@ -615,19 +601,17 @@
       <c r="E6" s="2">
         <v>22</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>43087</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>10</v>
+      <c r="B7" s="6" t="s">
+        <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="D7" s="2">
         <v>320</v>
@@ -635,19 +619,17 @@
       <c r="E7" s="2">
         <v>139</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="F7" s="1"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>42632</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>12</v>
+      <c r="B8" s="6" t="s">
+        <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D8" s="2">
         <v>240</v>
@@ -655,19 +637,17 @@
       <c r="E8" s="2">
         <v>22</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="F8" s="1"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>42296</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>14</v>
+      <c r="B9" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="D9" s="2">
         <v>204</v>
@@ -681,11 +661,11 @@
       <c r="A10" s="3">
         <v>41645</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>16</v>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="D10" s="2">
         <v>320</v>
@@ -693,19 +673,17 @@
       <c r="E10" s="2">
         <v>31</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>41575</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>18</v>
+      <c r="B11" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="D11" s="2">
         <v>32</v>
@@ -713,19 +691,17 @@
       <c r="E11" s="2">
         <v>28</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>41218</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>20</v>
+      <c r="B12" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="D12" s="2">
         <v>192</v>
@@ -733,19 +709,17 @@
       <c r="E12" s="2">
         <v>15</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>40616</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>4</v>
+      <c r="B13" s="6" t="s">
+        <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="D13" s="2">
         <v>224</v>
@@ -753,19 +727,17 @@
       <c r="E13" s="2">
         <v>28</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>40238</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>23</v>
+      <c r="B14" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="D14" s="2">
         <v>192</v>
@@ -774,18 +746,18 @@
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>39867</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>26</v>
+      <c r="B15" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D15" s="2">
         <v>224</v>
@@ -794,7 +766,7 @@
         <v>17</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -802,10 +774,10 @@
         <v>39664</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D16" s="2">
         <v>192</v>
@@ -814,7 +786,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -822,10 +794,10 @@
         <v>39090</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D17" s="2">
         <v>320</v>
@@ -834,7 +806,7 @@
         <v>44</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -842,10 +814,10 @@
         <v>38824</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D18" s="2">
         <v>224</v>
@@ -854,7 +826,7 @@
         <v>19</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -862,10 +834,10 @@
         <v>38530</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D19" s="2">
         <v>320</v>
@@ -874,7 +846,7 @@
         <v>18</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -882,10 +854,10 @@
         <v>38495</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D20" s="2">
         <v>32</v>
@@ -894,7 +866,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -902,10 +874,10 @@
         <v>38061</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2">
         <v>320</v>
@@ -914,7 +886,7 @@
         <v>31</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -922,10 +894,10 @@
         <v>37914</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D22" s="2">
         <v>190</v>
@@ -934,7 +906,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -942,10 +914,10 @@
         <v>37515</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D23" s="2">
         <v>416</v>
@@ -954,7 +926,7 @@
         <v>28</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -962,10 +934,10 @@
         <v>37102</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D24" s="2">
         <v>416</v>
@@ -974,7 +946,7 @@
         <v>30</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
@@ -982,10 +954,10 @@
         <v>36927</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D25" s="2">
         <v>192</v>
@@ -994,7 +966,7 @@
         <v>11</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
@@ -1002,10 +974,10 @@
         <v>36633</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D26" s="2">
         <v>320</v>
@@ -1014,7 +986,7 @@
         <v>18</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
@@ -1022,10 +994,10 @@
         <v>36241</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D27" s="2">
         <v>449</v>
@@ -1034,7 +1006,7 @@
         <v>133</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -1042,10 +1014,10 @@
         <v>36192</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D28" s="2">
         <v>32</v>
@@ -1054,7 +1026,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
@@ -1062,10 +1034,10 @@
         <v>36150</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="D29" s="2">
         <v>32</v>
@@ -1082,10 +1054,10 @@
         <v>36101</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D30" s="2">
         <v>32</v>
@@ -1102,10 +1074,10 @@
         <v>36059</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="D31" s="2">
         <v>32</v>
@@ -1122,10 +1094,10 @@
         <v>35919</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="D32" s="2">
         <v>192</v>
@@ -1134,7 +1106,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
@@ -1142,10 +1114,10 @@
         <v>35709</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D33" s="2">
         <v>192</v>
@@ -1154,7 +1126,7 @@
         <v>16</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -1162,10 +1134,10 @@
         <v>35317</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D34" s="2">
         <v>449</v>
@@ -1174,7 +1146,7 @@
         <v>133</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
@@ -1182,10 +1154,10 @@
         <v>35184</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D35" s="2">
         <v>192</v>
@@ -1202,10 +1174,10 @@
         <v>34610</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D36" s="2">
         <v>320</v>
@@ -1214,7 +1186,7 @@
         <v>44</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
@@ -1222,10 +1194,10 @@
         <v>34463</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D37" s="2">
         <v>192</v>
@@ -1234,7 +1206,7 @@
         <v>20</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
@@ -1242,10 +1214,10 @@
         <v>34281</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="D38" s="2">
         <v>192</v>
@@ -1254,7 +1226,7 @@
         <v>14</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
@@ -1262,10 +1234,10 @@
         <v>33889</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D39" s="2">
         <v>449</v>
@@ -1274,7 +1246,7 @@
         <v>133</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -1282,10 +1254,10 @@
         <v>33315</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D40" s="2">
         <v>320</v>
@@ -1294,7 +1266,7 @@
         <v>44</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
@@ -1302,10 +1274,10 @@
         <v>33280</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D41" s="2">
         <v>32</v>
@@ -1322,10 +1294,10 @@
         <v>33140</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="D42" s="2">
         <v>192</v>
@@ -1334,7 +1306,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
@@ -1342,10 +1314,10 @@
         <v>33042</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D43" s="2">
         <v>32</v>
@@ -1362,10 +1334,10 @@
         <v>32615</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D44" s="2">
         <v>320</v>
@@ -1374,7 +1346,7 @@
         <v>44</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
@@ -1382,10 +1354,10 @@
         <v>32370</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D45" s="2">
         <v>256</v>
@@ -1394,7 +1366,7 @@
         <v>20</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
@@ -1403,7 +1375,7 @@
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="2" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>1</v>
@@ -1412,7 +1384,7 @@
         <v>1</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
@@ -1425,75 +1397,75 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="B5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="B6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="B7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="B8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="B9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="B10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="B11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="B12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="B13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="B14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="B15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="B16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="F16" r:id="rId16" location="h=1:0-35:150" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="B17" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="F17" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="B18" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="F18" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="B19" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="F19" r:id="rId22" location="h=1:0-47:91" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="B20" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="F20" r:id="rId24" location="h=1:0-20:289" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="B21" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="F21" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="B22" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="F22" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="B23" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="F23" r:id="rId30" location="h=1:0-60:31" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="B24" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="F24" r:id="rId32" location="h=1:0-62:30" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="B25" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="F25" r:id="rId34" location="h=1:0-28:24" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="B26" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="F26" r:id="rId36" location="h=1:0-50:74" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="B27" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="F27" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="B28" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="F28" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="B29" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="B30" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="B31" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="B32" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="F32" r:id="rId45" location="h=9:0-9:173" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="B33" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="F33" r:id="rId47" location="h=1:0-5:233" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="B34" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="F34" r:id="rId49" location="h=3:0-3:186" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="B35" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="B36" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="F36" r:id="rId52" location="h=1:0-4:504" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="B37" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="F37" r:id="rId54" location="h=5:0-5:150" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="B38" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="F38" r:id="rId56" location="h=4:0-4:152" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="B39" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="F39" r:id="rId58" location="h=1:0-6:577" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="B40" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="F40" r:id="rId60" location="h=6:281-6:421" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="B41" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="B42" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="F42" r:id="rId63" location="h=4:0-4:130" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="B43" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="B44" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="F44" r:id="rId66" location="h=5:0-7:25" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="B45" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="F45" r:id="rId68" location="h=5:0-5:336" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="F46" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="B16" r:id="rId1" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="F16" r:id="rId2" location="h=1:0-35:150" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="B17" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="F17" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="B18" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="F18" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="B19" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="F19" r:id="rId8" location="h=1:0-47:91" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="B20" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="F20" r:id="rId10" location="h=1:0-20:289" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="B21" r:id="rId11" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="F21" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="B22" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="F22" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="B23" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="F23" r:id="rId16" location="h=1:0-60:31" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="B24" r:id="rId17" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="F24" r:id="rId18" location="h=1:0-62:30" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="B25" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="F25" r:id="rId20" location="h=1:0-28:24" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="B26" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="F26" r:id="rId22" location="h=1:0-50:74" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="B27" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="F27" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="B28" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="F28" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="B29" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="B30" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="B31" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="B32" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="F32" r:id="rId31" location="h=9:0-9:173" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="B33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="F33" r:id="rId33" location="h=1:0-5:233" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="B34" r:id="rId34" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="F34" r:id="rId35" location="h=3:0-3:186" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="B35" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="B36" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="F36" r:id="rId38" location="h=1:0-4:504" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="B37" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="F37" r:id="rId40" location="h=5:0-5:150" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="B38" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="F38" r:id="rId42" location="h=4:0-4:152" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="B39" r:id="rId43" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="F39" r:id="rId44" location="h=1:0-6:577" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="B40" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="F40" r:id="rId46" location="h=6:281-6:421" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="B41" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="B42" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="F42" r:id="rId49" location="h=4:0-4:130" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="B43" r:id="rId50" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="B44" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="F44" r:id="rId52" location="h=5:0-7:25" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="B45" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="F45" r:id="rId54" location="h=5:0-5:336" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="F46" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="B2" r:id="rId56" display="https://wol.jw.org/de/wol/publication/r10/lp-x/wcg" xr:uid="{438B671C-CE28-4C67-A662-F1708C83D91D}"/>
+    <hyperlink ref="B3" r:id="rId57" display="https://wol.jw.org/de/wol/publication/r10/lp-x/lfb" xr:uid="{D871F603-E0A5-4019-BF05-AF7285864A59}"/>
+    <hyperlink ref="B4" r:id="rId58" display="https://wol.jw.org/de/wol/publication/r10/lp-x/bt" xr:uid="{1782BFF0-E87A-45D4-A440-C40425352288}"/>
+    <hyperlink ref="B5" r:id="rId59" display="https://wol.jw.org/de/wol/publication/r10/lp-x/lff" xr:uid="{AEA45038-9C1E-4882-A97F-E2691C620A93}"/>
+    <hyperlink ref="B6" r:id="rId60" display="https://wol.jw.org/de/wol/publication/r10/lp-x/rr" xr:uid="{E3C74BB0-9262-488C-B6B0-BE641DB5984D}"/>
+    <hyperlink ref="B7" r:id="rId61" display="https://wol.jw.org/de/wol/publication/r10/lp-x/jy" xr:uid="{61A65EFA-7FAB-4ACC-83B6-0F6DF1164A83}"/>
+    <hyperlink ref="B8" r:id="rId62" display="https://wol.jw.org/de/wol/publication/r10/lp-x/kr" xr:uid="{85B70305-78C9-4E25-B52A-DE2A7E685091}"/>
+    <hyperlink ref="B9" r:id="rId63" display="https://wol.jw.org/de/wol/publication/r10/lp-x/ia" xr:uid="{75009524-6CF4-4CFA-99F4-FF121D4BD7D9}"/>
+    <hyperlink ref="B10" r:id="rId64" display="https://wol.jw.org/de/wol/publication/r10/lp-x/cl" xr:uid="{9CD62B75-FAF8-49FC-9474-C78913E8895C}"/>
+    <hyperlink ref="B11" r:id="rId65" display="https://wol.jw.org/de/wol/publication/r10/lp-x/jl" xr:uid="{6CA9BA42-5A6F-4867-A778-7A03BE55A2F1}"/>
+    <hyperlink ref="B12" r:id="rId66" display="https://wol.jw.org/de/wol/publication/r10/lp-x/jr" xr:uid="{BA787202-D01B-4A10-95C8-22038FB24783}"/>
+    <hyperlink ref="B13" r:id="rId67" display="https://wol.jw.org/de/wol/publication/r10/lp-x/bt" xr:uid="{EF4D93BB-CE19-4A26-AB3F-E8FD580CCFAE}"/>
+    <hyperlink ref="B14" r:id="rId68" display="https://wol.jw.org/de/wol/publication/r10/lp-x/cf" xr:uid="{01EFC84A-B143-4337-9E14-E2D85C66B518}"/>
+    <hyperlink ref="B15" r:id="rId69" display="https://wol.jw.org/en/wol/publication/r1/lp-e/lv" xr:uid="{F0C3F3AC-3B09-4947-B91C-4C042446383A}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId70"/>
